--- a/doc/рассчет/Топики и группы.xlsx
+++ b/doc/рассчет/Топики и группы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2679ADF3-CCDF-4824-97E4-1F7F683C156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6A119C-CE5D-425D-AA19-AB16D281F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9B9C20E4-F6B6-43F3-94A7-8AF849C87E43}"/>
   </bookViews>
